--- a/storage/templates/billing_template.xlsx
+++ b/storage/templates/billing_template.xlsx
@@ -1,24 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10608"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\oxytoxin\Sites\sksumpc\storage\templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lerry/Herd/sksumpc/storage/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8236895E-A3DF-4B35-BFDE-E7D864068CE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DC0B7F-BA6B-C741-A5E1-FE8241FDEA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2310" yWindow="2655" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2320" yWindow="2660" windowWidth="21600" windowHeight="11300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -26,9 +37,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>SKSU-MPC Regular Loan Billing Statement</t>
-  </si>
   <si>
     <t>NO.</t>
   </si>
@@ -44,13 +52,16 @@
   <si>
     <t>AMOUNT PAID</t>
   </si>
+  <si>
+    <t>SKSU-MPC Billing Statement</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -118,7 +129,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -130,24 +141,34 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -431,23 +452,23 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.5703125" customWidth="1"/>
-    <col min="2" max="2" width="23.42578125" customWidth="1"/>
-    <col min="3" max="3" width="54.42578125" customWidth="1"/>
-    <col min="4" max="4" width="27.5703125" style="12" customWidth="1"/>
-    <col min="5" max="5" width="26.42578125" style="12" customWidth="1"/>
+    <col min="1" max="1" width="8" style="10" customWidth="1"/>
+    <col min="2" max="2" width="23.5" style="10" customWidth="1"/>
+    <col min="3" max="3" width="47.5" style="10" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" style="11" customWidth="1"/>
+    <col min="5" max="5" width="19.83203125" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="63.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
-        <v>0</v>
+    <row r="1" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>5</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
@@ -460,21 +481,21 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="13" t="s">
         <v>4</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>5</v>
       </c>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
@@ -488,12 +509,12 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
+    <row r="3" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -506,12 +527,12 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
     </row>
-    <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
+    <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -524,22 +545,22 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
     </row>
-    <row r="5" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="6"/>
       <c r="B5" s="6"/>
       <c r="C5" s="6"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="9"/>
+      <c r="E6" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/storage/templates/billing_template.xlsx
+++ b/storage/templates/billing_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lerry/Herd/sksumpc/storage/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91DC0B7F-BA6B-C741-A5E1-FE8241FDEA4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46B65DC8-1CD0-6C48-8B05-AEBDFFC4FE00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2320" yWindow="2660" windowWidth="21600" windowHeight="11300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="21000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -131,7 +131,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -166,9 +166,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -455,10 +452,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8" style="10" customWidth="1"/>
-    <col min="2" max="2" width="23.5" style="10" customWidth="1"/>
+    <col min="2" max="2" width="25" style="10" customWidth="1"/>
     <col min="3" max="3" width="47.5" style="10" customWidth="1"/>
-    <col min="4" max="4" width="20.1640625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="19.83203125" style="11" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" style="11" customWidth="1"/>
+    <col min="5" max="5" width="21" style="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.2">
@@ -491,10 +488,10 @@
       <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="D2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F2" s="2"/>
